--- a/outputs/monitor_xlsx/20260417.xlsx
+++ b/outputs/monitor_xlsx/20260417.xlsx
@@ -810,12 +810,12 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-43.8億</t>
+          <t>-39.97億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-218.99億</t>
+          <t>-199.87億</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>131.72%</t>
+          <t>119.15%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -888,7 +888,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11169口</t>
+          <t>None口</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-43.8億</t>
+          <t>-39.97億</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-218.99億</t>
+          <t>-199.87億</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11169口</t>
+          <t>None口</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1316,10 +1316,10 @@
         <v>-29518</v>
       </c>
       <c r="H4" t="n">
-        <v>126415</v>
+        <v>-29518</v>
       </c>
       <c r="J4" t="n">
-        <v>1042</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>23302</v>
@@ -1328,14 +1328,11 @@
         <v>9069</v>
       </c>
       <c r="M4" t="n">
-        <v>45625</v>
+        <v>9069</v>
       </c>
       <c r="N4" t="n">
         <v>-4595232</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.9</v>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1371,13 +1368,13 @@
         <v>-446</v>
       </c>
       <c r="H5" t="n">
-        <v>-2227</v>
+        <v>-446</v>
       </c>
       <c r="I5" t="n">
         <v>-112</v>
       </c>
       <c r="J5" t="n">
-        <v>-190</v>
+        <v>-112</v>
       </c>
       <c r="K5" t="n">
         <v>70</v>
@@ -1386,14 +1383,11 @@
         <v>3039</v>
       </c>
       <c r="M5" t="n">
-        <v>14285</v>
+        <v>3039</v>
       </c>
       <c r="N5" t="n">
         <v>-78956</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.16</v>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1429,13 +1423,13 @@
         <v>-875</v>
       </c>
       <c r="H6" t="n">
-        <v>1249</v>
+        <v>-875</v>
       </c>
       <c r="I6" t="n">
         <v>357</v>
       </c>
       <c r="J6" t="n">
-        <v>-556</v>
+        <v>357</v>
       </c>
       <c r="K6" t="n">
         <v>216</v>
@@ -1444,14 +1438,11 @@
         <v>4804</v>
       </c>
       <c r="M6" t="n">
-        <v>24426</v>
+        <v>4804</v>
       </c>
       <c r="N6" t="n">
         <v>-649281</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.68</v>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1487,13 +1478,13 @@
         <v>-9383</v>
       </c>
       <c r="H7" t="n">
-        <v>20115</v>
+        <v>-9383</v>
       </c>
       <c r="I7" t="n">
         <v>-2186</v>
       </c>
       <c r="J7" t="n">
-        <v>-4041</v>
+        <v>-2186</v>
       </c>
       <c r="K7" t="n">
         <v>1074</v>
@@ -1502,14 +1493,11 @@
         <v>25670</v>
       </c>
       <c r="M7" t="n">
-        <v>134853</v>
+        <v>25670</v>
       </c>
       <c r="N7" t="n">
         <v>-6483016</v>
       </c>
-      <c r="O7" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1545,13 +1533,13 @@
         <v>125</v>
       </c>
       <c r="H8" t="n">
-        <v>635</v>
+        <v>125</v>
       </c>
       <c r="I8" t="n">
         <v>204</v>
       </c>
       <c r="J8" t="n">
-        <v>856</v>
+        <v>204</v>
       </c>
       <c r="K8" t="n">
         <v>140</v>
@@ -1560,14 +1548,11 @@
         <v>1415</v>
       </c>
       <c r="M8" t="n">
-        <v>7378</v>
+        <v>1415</v>
       </c>
       <c r="N8" t="n">
         <v>-140243</v>
       </c>
-      <c r="O8" t="n">
-        <v>5.77</v>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1603,13 +1588,13 @@
         <v>-1438</v>
       </c>
       <c r="H9" t="n">
-        <v>-4668</v>
+        <v>-1438</v>
       </c>
       <c r="I9" t="n">
         <v>275</v>
       </c>
       <c r="J9" t="n">
-        <v>1795</v>
+        <v>275</v>
       </c>
       <c r="K9" t="n">
         <v>121</v>
@@ -1618,14 +1603,11 @@
         <v>1817</v>
       </c>
       <c r="M9" t="n">
-        <v>9480</v>
+        <v>1817</v>
       </c>
       <c r="N9" t="n">
         <v>-106278</v>
       </c>
-      <c r="O9" t="n">
-        <v>12.24</v>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1661,13 +1643,13 @@
         <v>-49</v>
       </c>
       <c r="H10" t="n">
-        <v>586</v>
+        <v>-49</v>
       </c>
       <c r="I10" t="n">
         <v>-256</v>
       </c>
       <c r="J10" t="n">
-        <v>-335</v>
+        <v>-256</v>
       </c>
       <c r="K10" t="n">
         <v>111</v>
@@ -1676,14 +1658,11 @@
         <v>1859</v>
       </c>
       <c r="M10" t="n">
-        <v>9373</v>
+        <v>1859</v>
       </c>
       <c r="N10" t="n">
         <v>-89534</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1719,13 +1698,13 @@
         <v>-26</v>
       </c>
       <c r="H11" t="n">
-        <v>-1188</v>
+        <v>-26</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>-1018</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
         <v>76</v>
@@ -1734,14 +1713,11 @@
         <v>4740</v>
       </c>
       <c r="M11" t="n">
-        <v>21753</v>
+        <v>4740</v>
       </c>
       <c r="N11" t="n">
         <v>-19480</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1777,13 +1753,13 @@
         <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>90</v>
       </c>
       <c r="J12" t="n">
-        <v>288</v>
+        <v>90</v>
       </c>
       <c r="K12" t="n">
         <v>19</v>
@@ -1792,14 +1768,11 @@
         <v>304</v>
       </c>
       <c r="M12" t="n">
-        <v>1464</v>
+        <v>304</v>
       </c>
       <c r="N12" t="n">
         <v>-8988</v>
       </c>
-      <c r="O12" t="n">
-        <v>11.48</v>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1817,47 +1790,22 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1295</v>
-      </c>
-      <c r="G13" s="6" t="n">
+      <c r="C13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>361</v>
       </c>
-      <c r="H13" t="n">
-        <v>-467</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-926</v>
-      </c>
-      <c r="K13" t="n">
-        <v>99</v>
       </c>
       <c r="L13" t="n">
         <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>-30</v>
+        <v>44</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1875,47 +1823,22 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>644</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4446</v>
-      </c>
-      <c r="G14" s="6" t="n">
+      <c r="C14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>1979</v>
       </c>
-      <c r="H14" t="n">
-        <v>3474</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>119</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-158</v>
-      </c>
-      <c r="K14" t="n">
-        <v>156</v>
       </c>
       <c r="L14" t="n">
         <v>-266</v>
       </c>
       <c r="M14" t="n">
-        <v>3905</v>
+        <v>-266</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1933,47 +1856,22 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1215</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5909</v>
-      </c>
-      <c r="G15" s="7" t="n">
+      <c r="C15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>-848</v>
       </c>
-      <c r="H15" t="n">
-        <v>-3162</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>705</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1068</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>1268</v>
+        <v>106</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1991,47 +1889,22 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1620</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1101</v>
-      </c>
-      <c r="G16" s="7" t="n">
+      <c r="C16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>-216</v>
       </c>
-      <c r="H16" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>178</v>
-      </c>
-      <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>108</v>
       </c>
       <c r="M16" t="n">
-        <v>-4</v>
+        <v>108</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2067,13 +1940,13 @@
         <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I17" t="n">
         <v>-8</v>
       </c>
       <c r="J17" t="n">
-        <v>-72</v>
+        <v>-8</v>
       </c>
       <c r="K17" t="n">
         <v>29</v>
@@ -2082,15 +1955,177 @@
         <v>8980</v>
       </c>
       <c r="M17" t="n">
-        <v>45830</v>
+        <v>8980</v>
       </c>
       <c r="N17" t="n">
         <v>-21860</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.48</v>
-      </c>
       <c r="V17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>643</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4620</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>234</v>
+      </c>
+      <c r="H18" t="n">
+        <v>234</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-460</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-460</v>
+      </c>
+      <c r="K18" t="n">
+        <v>141</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34714</v>
+      </c>
+      <c r="M18" t="n">
+        <v>34714</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-393715</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>724</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25620</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-3207</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-3207</v>
+      </c>
+      <c r="I19" t="n">
+        <v>609</v>
+      </c>
+      <c r="J19" t="n">
+        <v>609</v>
+      </c>
+      <c r="K19" t="n">
+        <v>629</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9447</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9447</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-160712</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F20" t="n">
+        <v>16759</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>5340</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5340</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1284</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1284</v>
+      </c>
+      <c r="K20" t="n">
+        <v>285</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7864</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7864</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-400911</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
